--- a/livrables/marges_par_intergare.xlsx
+++ b/livrables/marges_par_intergare.xlsx
@@ -605,10 +605,10 @@
         <v>3.4</v>
       </c>
       <c r="N2" t="n">
-        <v>284.1</v>
+        <v>281.4</v>
       </c>
       <c r="O2" t="n">
-        <v>157.4</v>
+        <v>157</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -670,13 +670,13 @@
         <v>14</v>
       </c>
       <c r="M3" t="n">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
       <c r="N3" t="n">
-        <v>42.7</v>
+        <v>41.6</v>
       </c>
       <c r="O3" t="n">
-        <v>16.5</v>
+        <v>16.2</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -738,13 +738,13 @@
         <v>14</v>
       </c>
       <c r="M4" t="n">
-        <v>18</v>
+        <v>17.6</v>
       </c>
       <c r="N4" t="n">
-        <v>69.59999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>26.8</v>
+        <v>27.6</v>
       </c>
       <c r="P4" t="n">
         <v>8</v>
@@ -801,13 +801,13 @@
         <v>7</v>
       </c>
       <c r="M5" t="n">
-        <v>60.3</v>
+        <v>59.8</v>
       </c>
       <c r="N5" t="n">
-        <v>60.8</v>
+        <v>62.1</v>
       </c>
       <c r="O5" t="n">
-        <v>25.3</v>
+        <v>25.6</v>
       </c>
       <c r="P5" t="n">
         <v>16</v>
@@ -864,13 +864,13 @@
         <v>7</v>
       </c>
       <c r="M6" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>135.1</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>69.8</v>
+        <v>57.7</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -932,13 +932,13 @@
         <v>14</v>
       </c>
       <c r="M7" t="n">
-        <v>10.9</v>
+        <v>10.4</v>
       </c>
       <c r="N7" t="n">
-        <v>130.1</v>
+        <v>139.3</v>
       </c>
       <c r="O7" t="n">
-        <v>71.09999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1000,13 +1000,13 @@
         <v>26</v>
       </c>
       <c r="M8" t="n">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="N8" t="n">
-        <v>177</v>
+        <v>197.7</v>
       </c>
       <c r="O8" t="n">
-        <v>84.40000000000001</v>
+        <v>87.7</v>
       </c>
       <c r="P8" t="n">
         <v>2</v>
@@ -1068,13 +1068,13 @@
         <v>7</v>
       </c>
       <c r="M9" t="n">
-        <v>16.8</v>
+        <v>17.3</v>
       </c>
       <c r="N9" t="n">
-        <v>36.8</v>
+        <v>33.3</v>
       </c>
       <c r="O9" t="n">
-        <v>13.9</v>
+        <v>12.9</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
@@ -1131,13 +1131,13 @@
         <v>7</v>
       </c>
       <c r="M10" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="N10" t="n">
-        <v>33.2</v>
+        <v>33.8</v>
       </c>
       <c r="O10" t="n">
-        <v>14.1</v>
+        <v>14.3</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1194,13 +1194,13 @@
         <v>7</v>
       </c>
       <c r="M11" t="n">
-        <v>16.9</v>
+        <v>17.7</v>
       </c>
       <c r="N11" t="n">
-        <v>24</v>
+        <v>18.4</v>
       </c>
       <c r="O11" t="n">
-        <v>10.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1257,13 +1257,13 @@
         <v>7</v>
       </c>
       <c r="M12" t="n">
-        <v>18.3</v>
+        <v>21.6</v>
       </c>
       <c r="N12" t="n">
-        <v>42</v>
+        <v>20.6</v>
       </c>
       <c r="O12" t="n">
-        <v>16.5</v>
+        <v>9.5</v>
       </c>
       <c r="P12" t="n">
         <v>5</v>
@@ -1328,10 +1328,10 @@
         <v>6.6</v>
       </c>
       <c r="N13" t="n">
-        <v>158.4</v>
+        <v>157.7</v>
       </c>
       <c r="O13" t="n">
-        <v>67.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="P13" t="n">
         <v>1</v>
@@ -1396,10 +1396,10 @@
         <v>18.5</v>
       </c>
       <c r="N14" t="n">
-        <v>51.4</v>
+        <v>51.2</v>
       </c>
       <c r="O14" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="P14" t="n">
         <v>4</v>
@@ -1456,13 +1456,13 @@
         <v>11</v>
       </c>
       <c r="M15" t="n">
-        <v>18.5</v>
+        <v>18.1</v>
       </c>
       <c r="N15" t="n">
-        <v>62.5</v>
+        <v>65.5</v>
       </c>
       <c r="O15" t="n">
-        <v>25.4</v>
+        <v>26.2</v>
       </c>
       <c r="P15" t="n">
         <v>3</v>
@@ -1519,13 +1519,13 @@
         <v>4</v>
       </c>
       <c r="M16" t="n">
-        <v>17.7</v>
+        <v>17.5</v>
       </c>
       <c r="N16" t="n">
-        <v>44.4</v>
+        <v>45.5</v>
       </c>
       <c r="O16" t="n">
-        <v>17.1</v>
+        <v>17.4</v>
       </c>
       <c r="P16" t="n">
         <v>2</v>
@@ -1582,13 +1582,13 @@
         <v>4</v>
       </c>
       <c r="M17" t="n">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="N17" t="n">
-        <v>40.2</v>
+        <v>42.9</v>
       </c>
       <c r="O17" t="n">
-        <v>16.2</v>
+        <v>17</v>
       </c>
       <c r="P17" t="n">
         <v>2</v>
@@ -1645,13 +1645,13 @@
         <v>6</v>
       </c>
       <c r="M18" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="N18" t="n">
-        <v>44.3</v>
+        <v>44.5</v>
       </c>
       <c r="O18" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="P18" t="n">
         <v>1</v>
@@ -1711,7 +1711,7 @@
         <v>13.2</v>
       </c>
       <c r="N19" t="n">
-        <v>36.3</v>
+        <v>36.1</v>
       </c>
       <c r="O19" t="n">
         <v>13.7</v>
@@ -1837,7 +1837,7 @@
         <v>18.7</v>
       </c>
       <c r="N21" t="n">
-        <v>33.6</v>
+        <v>33.3</v>
       </c>
       <c r="O21" t="n">
         <v>12.5</v>
@@ -1897,13 +1897,13 @@
         <v>6</v>
       </c>
       <c r="M22" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="N22" t="n">
-        <v>69.8</v>
+        <v>97</v>
       </c>
       <c r="O22" t="n">
-        <v>30.4</v>
+        <v>36.4</v>
       </c>
       <c r="P22" t="n">
         <v>1</v>
@@ -1960,13 +1960,13 @@
         <v>5</v>
       </c>
       <c r="M23" t="n">
-        <v>19.6</v>
+        <v>19</v>
       </c>
       <c r="N23" t="n">
-        <v>32.8</v>
+        <v>36.6</v>
       </c>
       <c r="O23" t="n">
-        <v>12.7</v>
+        <v>13.8</v>
       </c>
       <c r="P23" t="n">
         <v>1</v>
@@ -2026,10 +2026,10 @@
         <v>11.4</v>
       </c>
       <c r="N24" t="n">
-        <v>49.6</v>
+        <v>48.7</v>
       </c>
       <c r="O24" t="n">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
       <c r="P24" t="n">
         <v>8</v>
@@ -2091,13 +2091,13 @@
         <v>17</v>
       </c>
       <c r="M25" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="N25" t="n">
-        <v>123.2</v>
+        <v>127.8</v>
       </c>
       <c r="O25" t="n">
-        <v>49.4</v>
+        <v>50.2</v>
       </c>
       <c r="P25" t="n">
         <v>1</v>
@@ -2159,13 +2159,13 @@
         <v>10</v>
       </c>
       <c r="M26" t="n">
-        <v>13.4</v>
+        <v>13</v>
       </c>
       <c r="N26" t="n">
-        <v>75</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>29.6</v>
+        <v>31</v>
       </c>
       <c r="P26" t="n">
         <v>1</v>
@@ -2230,10 +2230,10 @@
         <v>8.6</v>
       </c>
       <c r="N27" t="n">
-        <v>50.4</v>
+        <v>50.8</v>
       </c>
       <c r="O27" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="P27" t="n">
         <v>1</v>
@@ -2295,13 +2295,13 @@
         <v>9</v>
       </c>
       <c r="M28" t="n">
-        <v>16</v>
+        <v>15.6</v>
       </c>
       <c r="N28" t="n">
-        <v>74.8</v>
+        <v>79.3</v>
       </c>
       <c r="O28" t="n">
-        <v>30.6</v>
+        <v>31.6</v>
       </c>
       <c r="P28" t="n">
         <v>2</v>
@@ -2358,10 +2358,10 @@
         <v>9</v>
       </c>
       <c r="M29" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="N29" t="n">
-        <v>67.40000000000001</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="O29" t="n">
         <v>26.4</v>
@@ -2424,10 +2424,10 @@
         <v>5.6</v>
       </c>
       <c r="N30" t="n">
-        <v>114.1</v>
+        <v>113</v>
       </c>
       <c r="O30" t="n">
-        <v>42.4</v>
+        <v>42.2</v>
       </c>
       <c r="P30" t="n">
         <v>1</v>
@@ -2484,13 +2484,13 @@
         <v>6</v>
       </c>
       <c r="M31" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="N31" t="n">
-        <v>76.59999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="O31" t="n">
-        <v>29.1</v>
+        <v>29.8</v>
       </c>
       <c r="P31" t="n">
         <v>1</v>
@@ -2613,7 +2613,7 @@
         <v>20.4</v>
       </c>
       <c r="N33" t="n">
-        <v>59.3</v>
+        <v>59.2</v>
       </c>
       <c r="O33" t="n">
         <v>22.2</v>
@@ -2676,10 +2676,10 @@
         <v>26.4</v>
       </c>
       <c r="N34" t="n">
-        <v>68.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="O34" t="n">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="P34" t="n">
         <v>7</v>
@@ -2739,10 +2739,10 @@
         <v>9.699999999999999</v>
       </c>
       <c r="N35" t="n">
-        <v>131.6</v>
+        <v>132.7</v>
       </c>
       <c r="O35" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -2798,13 +2798,13 @@
         <v>2</v>
       </c>
       <c r="M36" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N36" t="n">
-        <v>235.7</v>
+        <v>231.4</v>
       </c>
       <c r="O36" t="n">
-        <v>87</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -2860,13 +2860,13 @@
         <v>2</v>
       </c>
       <c r="M37" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="N37" t="n">
-        <v>107.2</v>
+        <v>105.6</v>
       </c>
       <c r="O37" t="n">
-        <v>39.9</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="38">
@@ -2917,13 +2917,13 @@
         <v>2</v>
       </c>
       <c r="M38" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="N38" t="n">
-        <v>83.2</v>
+        <v>84.3</v>
       </c>
       <c r="O38" t="n">
-        <v>31.9</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="39">
@@ -2974,10 +2974,10 @@
         <v>2</v>
       </c>
       <c r="M39" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="N39" t="n">
-        <v>166.3</v>
+        <v>165.8</v>
       </c>
       <c r="O39" t="n">
         <v>62</v>
@@ -3031,13 +3031,13 @@
         <v>2</v>
       </c>
       <c r="M40" t="n">
-        <v>15.6</v>
+        <v>15.4</v>
       </c>
       <c r="N40" t="n">
-        <v>172</v>
+        <v>176.3</v>
       </c>
       <c r="O40" t="n">
-        <v>65.40000000000001</v>
+        <v>66</v>
       </c>
     </row>
     <row r="41">
@@ -3088,13 +3088,13 @@
         <v>2</v>
       </c>
       <c r="M41" t="n">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="N41" t="n">
-        <v>259</v>
+        <v>233.7</v>
       </c>
       <c r="O41" t="n">
-        <v>108.2</v>
+        <v>105.1</v>
       </c>
     </row>
     <row r="42">
@@ -3145,13 +3145,13 @@
         <v>2</v>
       </c>
       <c r="M42" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="N42" t="n">
-        <v>258.6</v>
+        <v>262.7</v>
       </c>
       <c r="O42" t="n">
-        <v>101.5</v>
+        <v>102</v>
       </c>
     </row>
     <row r="43">
@@ -3202,13 +3202,13 @@
         <v>2</v>
       </c>
       <c r="M43" t="n">
-        <v>11.9</v>
+        <v>11.5</v>
       </c>
       <c r="N43" t="n">
-        <v>85.40000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="O43" t="n">
-        <v>32.9</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="44">
@@ -3259,13 +3259,13 @@
         <v>2</v>
       </c>
       <c r="M44" t="n">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="N44" t="n">
-        <v>83.8</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="O44" t="n">
-        <v>32</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="45">
@@ -3316,13 +3316,13 @@
         <v>26</v>
       </c>
       <c r="M45" t="n">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="N45" t="n">
-        <v>176.7</v>
+        <v>197.7</v>
       </c>
       <c r="O45" t="n">
-        <v>84.40000000000001</v>
+        <v>87.7</v>
       </c>
       <c r="P45" t="n">
         <v>2</v>
@@ -3455,7 +3455,7 @@
         <v>34.4</v>
       </c>
       <c r="N47" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="O47" t="n">
         <v>12.1</v>
@@ -3515,13 +3515,13 @@
         <v>4</v>
       </c>
       <c r="M48" t="n">
-        <v>17</v>
+        <v>16.8</v>
       </c>
       <c r="N48" t="n">
-        <v>49.7</v>
+        <v>51.8</v>
       </c>
       <c r="O48" t="n">
-        <v>18.8</v>
+        <v>19.3</v>
       </c>
       <c r="P48" t="n">
         <v>2</v>
@@ -3583,13 +3583,13 @@
         <v>4</v>
       </c>
       <c r="M49" t="n">
-        <v>14.9</v>
+        <v>14.6</v>
       </c>
       <c r="N49" t="n">
-        <v>37.4</v>
+        <v>40.1</v>
       </c>
       <c r="O49" t="n">
-        <v>15.4</v>
+        <v>16.2</v>
       </c>
       <c r="P49" t="n">
         <v>2</v>
@@ -3654,7 +3654,7 @@
         <v>13.8</v>
       </c>
       <c r="N50" t="n">
-        <v>44.7</v>
+        <v>44.5</v>
       </c>
       <c r="O50" t="n">
         <v>17.4</v>
@@ -3722,10 +3722,10 @@
         <v>13.2</v>
       </c>
       <c r="N51" t="n">
-        <v>36.1</v>
+        <v>35.9</v>
       </c>
       <c r="O51" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="P51" t="n">
         <v>0</v>
@@ -3855,10 +3855,10 @@
         <v>7</v>
       </c>
       <c r="M53" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="N53" t="n">
-        <v>33.5</v>
+        <v>33.3</v>
       </c>
       <c r="O53" t="n">
         <v>12.5</v>
@@ -3923,13 +3923,13 @@
         <v>6</v>
       </c>
       <c r="M54" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="N54" t="n">
-        <v>72.7</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="O54" t="n">
-        <v>31.2</v>
+        <v>36.5</v>
       </c>
       <c r="P54" t="n">
         <v>1</v>
@@ -3991,13 +3991,13 @@
         <v>5</v>
       </c>
       <c r="M55" t="n">
-        <v>19.6</v>
+        <v>19</v>
       </c>
       <c r="N55" t="n">
-        <v>32.4</v>
+        <v>36.7</v>
       </c>
       <c r="O55" t="n">
-        <v>12.6</v>
+        <v>13.9</v>
       </c>
       <c r="P55" t="n">
         <v>1</v>
@@ -4062,10 +4062,10 @@
         <v>11.4</v>
       </c>
       <c r="N56" t="n">
-        <v>49.2</v>
+        <v>48.7</v>
       </c>
       <c r="O56" t="n">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="P56" t="n">
         <v>8</v>
@@ -4135,10 +4135,10 @@
         <v>7.9</v>
       </c>
       <c r="N57" t="n">
-        <v>127.6</v>
+        <v>128.5</v>
       </c>
       <c r="O57" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="P57" t="n">
         <v>1</v>

--- a/livrables/marges_par_intergare.xlsx
+++ b/livrables/marges_par_intergare.xlsx
@@ -442,7 +442,7 @@
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="21" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>t_base_S1cap160_min</t>
+          <t>t_base_cap160_min</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">

--- a/livrables/marges_par_intergare.xlsx
+++ b/livrables/marges_par_intergare.xlsx
@@ -602,13 +602,13 @@
         <v>16</v>
       </c>
       <c r="M2" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N2" t="n">
-        <v>281.4</v>
+        <v>244</v>
       </c>
       <c r="O2" t="n">
-        <v>157</v>
+        <v>150.9</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -670,13 +670,13 @@
         <v>14</v>
       </c>
       <c r="M3" t="n">
-        <v>18.4</v>
+        <v>19.1</v>
       </c>
       <c r="N3" t="n">
-        <v>41.6</v>
+        <v>36.1</v>
       </c>
       <c r="O3" t="n">
-        <v>16.2</v>
+        <v>14.6</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -738,13 +738,13 @@
         <v>14</v>
       </c>
       <c r="M4" t="n">
-        <v>17.6</v>
+        <v>18.4</v>
       </c>
       <c r="N4" t="n">
-        <v>73.40000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>27.6</v>
+        <v>25.8</v>
       </c>
       <c r="P4" t="n">
         <v>8</v>
@@ -801,13 +801,13 @@
         <v>7</v>
       </c>
       <c r="M5" t="n">
-        <v>59.8</v>
+        <v>62.9</v>
       </c>
       <c r="N5" t="n">
-        <v>62.1</v>
+        <v>54.2</v>
       </c>
       <c r="O5" t="n">
-        <v>25.6</v>
+        <v>23.5</v>
       </c>
       <c r="P5" t="n">
         <v>16</v>
@@ -864,13 +864,13 @@
         <v>7</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="N6" t="n">
-        <v>90.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>57.7</v>
+        <v>47.9</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -932,13 +932,13 @@
         <v>14</v>
       </c>
       <c r="M7" t="n">
-        <v>10.4</v>
+        <v>12.2</v>
       </c>
       <c r="N7" t="n">
-        <v>139.3</v>
+        <v>105.7</v>
       </c>
       <c r="O7" t="n">
-        <v>73.2</v>
+        <v>64.7</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1000,13 +1000,13 @@
         <v>26</v>
       </c>
       <c r="M8" t="n">
-        <v>7.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>197.7</v>
+        <v>181.4</v>
       </c>
       <c r="O8" t="n">
-        <v>87.7</v>
+        <v>85.2</v>
       </c>
       <c r="P8" t="n">
         <v>2</v>
@@ -1068,13 +1068,13 @@
         <v>7</v>
       </c>
       <c r="M9" t="n">
-        <v>17.3</v>
+        <v>17.8</v>
       </c>
       <c r="N9" t="n">
-        <v>33.3</v>
+        <v>29.3</v>
       </c>
       <c r="O9" t="n">
-        <v>12.9</v>
+        <v>11.7</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
@@ -1131,13 +1131,13 @@
         <v>7</v>
       </c>
       <c r="M10" t="n">
-        <v>15.7</v>
+        <v>16.3</v>
       </c>
       <c r="N10" t="n">
-        <v>33.8</v>
+        <v>28.6</v>
       </c>
       <c r="O10" t="n">
-        <v>14.3</v>
+        <v>12.6</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1194,13 +1194,13 @@
         <v>7</v>
       </c>
       <c r="M11" t="n">
-        <v>17.7</v>
+        <v>18.5</v>
       </c>
       <c r="N11" t="n">
-        <v>18.4</v>
+        <v>13.4</v>
       </c>
       <c r="O11" t="n">
-        <v>8.300000000000001</v>
+        <v>6.3</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1257,13 +1257,13 @@
         <v>7</v>
       </c>
       <c r="M12" t="n">
-        <v>21.6</v>
+        <v>22.4</v>
       </c>
       <c r="N12" t="n">
-        <v>20.6</v>
+        <v>16.1</v>
       </c>
       <c r="O12" t="n">
-        <v>9.5</v>
+        <v>7.7</v>
       </c>
       <c r="P12" t="n">
         <v>5</v>
@@ -1325,13 +1325,13 @@
         <v>21</v>
       </c>
       <c r="M13" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="N13" t="n">
-        <v>157.7</v>
+        <v>119.1</v>
       </c>
       <c r="O13" t="n">
-        <v>67.59999999999999</v>
+        <v>60.1</v>
       </c>
       <c r="P13" t="n">
         <v>1</v>
@@ -1393,13 +1393,13 @@
         <v>11</v>
       </c>
       <c r="M14" t="n">
-        <v>18.5</v>
+        <v>19.1</v>
       </c>
       <c r="N14" t="n">
-        <v>51.2</v>
+        <v>46.9</v>
       </c>
       <c r="O14" t="n">
-        <v>19.2</v>
+        <v>18.1</v>
       </c>
       <c r="P14" t="n">
         <v>4</v>
@@ -1456,13 +1456,13 @@
         <v>11</v>
       </c>
       <c r="M15" t="n">
-        <v>18.1</v>
+        <v>18.7</v>
       </c>
       <c r="N15" t="n">
-        <v>65.5</v>
+        <v>60.7</v>
       </c>
       <c r="O15" t="n">
-        <v>26.2</v>
+        <v>25</v>
       </c>
       <c r="P15" t="n">
         <v>3</v>
@@ -1519,13 +1519,13 @@
         <v>4</v>
       </c>
       <c r="M16" t="n">
-        <v>17.5</v>
+        <v>18.6</v>
       </c>
       <c r="N16" t="n">
-        <v>45.5</v>
+        <v>37.5</v>
       </c>
       <c r="O16" t="n">
-        <v>17.4</v>
+        <v>15.2</v>
       </c>
       <c r="P16" t="n">
         <v>2</v>
@@ -1582,13 +1582,13 @@
         <v>4</v>
       </c>
       <c r="M17" t="n">
-        <v>14.3</v>
+        <v>15.7</v>
       </c>
       <c r="N17" t="n">
-        <v>42.9</v>
+        <v>30.8</v>
       </c>
       <c r="O17" t="n">
-        <v>17</v>
+        <v>13.3</v>
       </c>
       <c r="P17" t="n">
         <v>2</v>
@@ -1645,13 +1645,13 @@
         <v>6</v>
       </c>
       <c r="M18" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="O18" t="n">
         <v>13.8</v>
-      </c>
-      <c r="N18" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="O18" t="n">
-        <v>17.4</v>
       </c>
       <c r="P18" t="n">
         <v>1</v>
@@ -1708,13 +1708,13 @@
         <v>6</v>
       </c>
       <c r="M19" t="n">
-        <v>13.2</v>
+        <v>13.6</v>
       </c>
       <c r="N19" t="n">
-        <v>36.1</v>
+        <v>32.6</v>
       </c>
       <c r="O19" t="n">
-        <v>13.7</v>
+        <v>12.7</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -1771,13 +1771,13 @@
         <v>7</v>
       </c>
       <c r="M20" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="N20" t="n">
-        <v>65.09999999999999</v>
+        <v>62.1</v>
       </c>
       <c r="O20" t="n">
-        <v>24.3</v>
+        <v>23.6</v>
       </c>
       <c r="P20" t="n">
         <v>1</v>
@@ -1834,13 +1834,13 @@
         <v>7</v>
       </c>
       <c r="M21" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="N21" t="n">
-        <v>33.3</v>
+        <v>32.6</v>
       </c>
       <c r="O21" t="n">
-        <v>12.5</v>
+        <v>12.3</v>
       </c>
       <c r="P21" t="n">
         <v>1</v>
@@ -1897,13 +1897,13 @@
         <v>6</v>
       </c>
       <c r="M22" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="N22" t="n">
-        <v>97</v>
+        <v>84.2</v>
       </c>
       <c r="O22" t="n">
-        <v>36.4</v>
+        <v>33.8</v>
       </c>
       <c r="P22" t="n">
         <v>1</v>
@@ -1960,13 +1960,13 @@
         <v>5</v>
       </c>
       <c r="M23" t="n">
-        <v>19</v>
+        <v>20.8</v>
       </c>
       <c r="N23" t="n">
-        <v>36.6</v>
+        <v>24.8</v>
       </c>
       <c r="O23" t="n">
-        <v>13.8</v>
+        <v>10.3</v>
       </c>
       <c r="P23" t="n">
         <v>1</v>
@@ -2023,13 +2023,13 @@
         <v>16</v>
       </c>
       <c r="M24" t="n">
-        <v>11.4</v>
+        <v>12.3</v>
       </c>
       <c r="N24" t="n">
-        <v>48.7</v>
+        <v>38.7</v>
       </c>
       <c r="O24" t="n">
-        <v>18.2</v>
+        <v>15.5</v>
       </c>
       <c r="P24" t="n">
         <v>8</v>
@@ -2091,13 +2091,13 @@
         <v>17</v>
       </c>
       <c r="M25" t="n">
-        <v>7.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>127.8</v>
+        <v>107.2</v>
       </c>
       <c r="O25" t="n">
-        <v>50.2</v>
+        <v>46.3</v>
       </c>
       <c r="P25" t="n">
         <v>1</v>
@@ -2159,13 +2159,13 @@
         <v>10</v>
       </c>
       <c r="M26" t="n">
-        <v>13</v>
+        <v>13.3</v>
       </c>
       <c r="N26" t="n">
-        <v>81.40000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="O26" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P26" t="n">
         <v>1</v>
@@ -2295,13 +2295,13 @@
         <v>9</v>
       </c>
       <c r="M28" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="N28" t="n">
-        <v>79.3</v>
+        <v>67.3</v>
       </c>
       <c r="O28" t="n">
-        <v>31.6</v>
+        <v>28.8</v>
       </c>
       <c r="P28" t="n">
         <v>2</v>
@@ -2358,13 +2358,13 @@
         <v>9</v>
       </c>
       <c r="M29" t="n">
-        <v>16.8</v>
+        <v>17.6</v>
       </c>
       <c r="N29" t="n">
-        <v>67.09999999999999</v>
+        <v>59.2</v>
       </c>
       <c r="O29" t="n">
-        <v>26.4</v>
+        <v>24.4</v>
       </c>
       <c r="P29" t="n">
         <v>2</v>
@@ -2421,13 +2421,13 @@
         <v>6</v>
       </c>
       <c r="M30" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="N30" t="n">
-        <v>113</v>
+        <v>107.7</v>
       </c>
       <c r="O30" t="n">
-        <v>42.2</v>
+        <v>41.2</v>
       </c>
       <c r="P30" t="n">
         <v>1</v>
@@ -2484,13 +2484,13 @@
         <v>6</v>
       </c>
       <c r="M31" t="n">
-        <v>11.4</v>
+        <v>11.7</v>
       </c>
       <c r="N31" t="n">
-        <v>79.8</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="O31" t="n">
-        <v>29.8</v>
+        <v>28.8</v>
       </c>
       <c r="P31" t="n">
         <v>1</v>
@@ -2547,13 +2547,13 @@
         <v>6</v>
       </c>
       <c r="M32" t="n">
-        <v>18.4</v>
+        <v>18.8</v>
       </c>
       <c r="N32" t="n">
-        <v>62.9</v>
+        <v>59.3</v>
       </c>
       <c r="O32" t="n">
-        <v>23.5</v>
+        <v>22.7</v>
       </c>
       <c r="P32" t="n">
         <v>4</v>
@@ -2736,13 +2736,13 @@
         <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>9.699999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="N35" t="n">
-        <v>132.7</v>
+        <v>118</v>
       </c>
       <c r="O35" t="n">
-        <v>50</v>
+        <v>47.5</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -2917,13 +2917,13 @@
         <v>2</v>
       </c>
       <c r="M38" t="n">
-        <v>11.9</v>
+        <v>13</v>
       </c>
       <c r="N38" t="n">
-        <v>84.3</v>
+        <v>69.7</v>
       </c>
       <c r="O38" t="n">
-        <v>32.1</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="39">
@@ -2974,13 +2974,13 @@
         <v>2</v>
       </c>
       <c r="M39" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="N39" t="n">
-        <v>165.8</v>
+        <v>161.7</v>
       </c>
       <c r="O39" t="n">
-        <v>62</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="40">
@@ -3031,13 +3031,13 @@
         <v>2</v>
       </c>
       <c r="M40" t="n">
-        <v>15.4</v>
+        <v>15.8</v>
       </c>
       <c r="N40" t="n">
-        <v>176.3</v>
+        <v>169.6</v>
       </c>
       <c r="O40" t="n">
-        <v>66</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -3088,13 +3088,13 @@
         <v>2</v>
       </c>
       <c r="M41" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="N41" t="n">
-        <v>233.7</v>
+        <v>224.3</v>
       </c>
       <c r="O41" t="n">
-        <v>105.1</v>
+        <v>103.7</v>
       </c>
     </row>
     <row r="42">
@@ -3145,13 +3145,13 @@
         <v>2</v>
       </c>
       <c r="M42" t="n">
-        <v>13.4</v>
+        <v>13.9</v>
       </c>
       <c r="N42" t="n">
-        <v>262.7</v>
+        <v>248.1</v>
       </c>
       <c r="O42" t="n">
-        <v>102</v>
+        <v>100.3</v>
       </c>
     </row>
     <row r="43">
@@ -3202,13 +3202,13 @@
         <v>2</v>
       </c>
       <c r="M43" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="N43" t="n">
-        <v>91.5</v>
+        <v>82.7</v>
       </c>
       <c r="O43" t="n">
-        <v>34.1</v>
+        <v>32.3</v>
       </c>
     </row>
     <row r="44">
@@ -3316,13 +3316,13 @@
         <v>26</v>
       </c>
       <c r="M45" t="n">
-        <v>7.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="N45" t="n">
-        <v>197.7</v>
+        <v>181.5</v>
       </c>
       <c r="O45" t="n">
-        <v>87.7</v>
+        <v>85.2</v>
       </c>
       <c r="P45" t="n">
         <v>2</v>
@@ -3389,13 +3389,13 @@
         <v>12</v>
       </c>
       <c r="M46" t="n">
-        <v>35.6</v>
+        <v>36.6</v>
       </c>
       <c r="N46" t="n">
-        <v>34.9</v>
+        <v>31.2</v>
       </c>
       <c r="O46" t="n">
-        <v>13.1</v>
+        <v>12</v>
       </c>
       <c r="P46" t="n">
         <v>2</v>
@@ -3452,13 +3452,13 @@
         <v>4</v>
       </c>
       <c r="M47" t="n">
-        <v>34.4</v>
+        <v>35.2</v>
       </c>
       <c r="N47" t="n">
-        <v>32.4</v>
+        <v>29.3</v>
       </c>
       <c r="O47" t="n">
-        <v>12.1</v>
+        <v>11.2</v>
       </c>
       <c r="P47" t="n">
         <v>2</v>
@@ -3515,13 +3515,13 @@
         <v>4</v>
       </c>
       <c r="M48" t="n">
-        <v>16.8</v>
+        <v>17.3</v>
       </c>
       <c r="N48" t="n">
-        <v>51.8</v>
+        <v>47.1</v>
       </c>
       <c r="O48" t="n">
-        <v>19.3</v>
+        <v>18.1</v>
       </c>
       <c r="P48" t="n">
         <v>2</v>
@@ -3583,13 +3583,13 @@
         <v>4</v>
       </c>
       <c r="M49" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="N49" t="n">
-        <v>40.1</v>
+        <v>28.5</v>
       </c>
       <c r="O49" t="n">
-        <v>16.2</v>
+        <v>12.5</v>
       </c>
       <c r="P49" t="n">
         <v>2</v>
@@ -3651,13 +3651,13 @@
         <v>6</v>
       </c>
       <c r="M50" t="n">
-        <v>13.8</v>
+        <v>15</v>
       </c>
       <c r="N50" t="n">
-        <v>44.5</v>
+        <v>32.9</v>
       </c>
       <c r="O50" t="n">
-        <v>17.4</v>
+        <v>13.9</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
@@ -3719,13 +3719,13 @@
         <v>6</v>
       </c>
       <c r="M51" t="n">
-        <v>13.2</v>
+        <v>13.6</v>
       </c>
       <c r="N51" t="n">
-        <v>35.9</v>
+        <v>32.1</v>
       </c>
       <c r="O51" t="n">
-        <v>13.6</v>
+        <v>12.5</v>
       </c>
       <c r="P51" t="n">
         <v>0</v>
@@ -3787,13 +3787,13 @@
         <v>7</v>
       </c>
       <c r="M52" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="N52" t="n">
-        <v>65.09999999999999</v>
+        <v>62.2</v>
       </c>
       <c r="O52" t="n">
-        <v>24.3</v>
+        <v>23.6</v>
       </c>
       <c r="P52" t="n">
         <v>1</v>
@@ -3855,13 +3855,13 @@
         <v>7</v>
       </c>
       <c r="M53" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="N53" t="n">
-        <v>33.3</v>
+        <v>32.4</v>
       </c>
       <c r="O53" t="n">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="P53" t="n">
         <v>1</v>
@@ -3923,13 +3923,13 @@
         <v>6</v>
       </c>
       <c r="M54" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="N54" t="n">
-        <v>97.09999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="O54" t="n">
-        <v>36.5</v>
+        <v>33.9</v>
       </c>
       <c r="P54" t="n">
         <v>1</v>
@@ -3991,13 +3991,13 @@
         <v>5</v>
       </c>
       <c r="M55" t="n">
-        <v>19</v>
+        <v>20.8</v>
       </c>
       <c r="N55" t="n">
-        <v>36.7</v>
+        <v>25</v>
       </c>
       <c r="O55" t="n">
-        <v>13.9</v>
+        <v>10.3</v>
       </c>
       <c r="P55" t="n">
         <v>1</v>
@@ -4059,13 +4059,13 @@
         <v>16</v>
       </c>
       <c r="M56" t="n">
-        <v>11.4</v>
+        <v>12.2</v>
       </c>
       <c r="N56" t="n">
-        <v>48.7</v>
+        <v>38.8</v>
       </c>
       <c r="O56" t="n">
-        <v>18.1</v>
+        <v>15.5</v>
       </c>
       <c r="P56" t="n">
         <v>8</v>
@@ -4132,13 +4132,13 @@
         <v>17</v>
       </c>
       <c r="M57" t="n">
-        <v>7.9</v>
+        <v>8.6</v>
       </c>
       <c r="N57" t="n">
-        <v>128.5</v>
+        <v>108.4</v>
       </c>
       <c r="O57" t="n">
-        <v>50.3</v>
+        <v>46.5</v>
       </c>
       <c r="P57" t="n">
         <v>1</v>

--- a/livrables/marges_par_intergare.xlsx
+++ b/livrables/marges_par_intergare.xlsx
@@ -880,7 +880,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>adjacente au pont de Québec</t>
+          <t>bloc urbain (pont de Québec)</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>bloc urbain (pont de Québec)</t>
+          <t>bloc urbain (gare du Palais)</t>
         </is>
       </c>
     </row>
